--- a/BWI/bestwine_output/bestwine_Bosnia.xlsx
+++ b/BWI/bestwine_output/bestwine_Bosnia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA62"/>
+  <dimension ref="A1:AA63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7253,6 +7253,119 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Union Foods D.o.o. Citluk</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Union Foods D.o.o. Citluk</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>20164</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Međugorje</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Hercegovačko-neretvanski kanton</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Gospodarska zona, Tromeđa VI br.7</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>88266</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://union-foods.com</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>info@union-foods.com</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>+387 36 653-450</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>4227040010008</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/unionfoodsdoo</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/union_foods/</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/unionfoods</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>Ilija Barbaric</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Director</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilija-barbaric-1137a43a/?originalSubdomain=ba</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
